--- a/training_forms/044_workplace_hazard_identification_training_form--training_forms.xlsx
+++ b/training_forms/044_workplace_hazard_identification_training_form--training_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1150,8 +1150,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'risk',_'value':_'risk'}</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Risk', 'value': 'Risk'}</t>
+          <t>Risk</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'hazard',_'value':_'hazard'}</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Hazard', 'value': 'Hazard'}</t>
+          <t>Hazard</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'injury',_'value':_'injury'}</t>
+          <t>injury</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Injury', 'value': 'Injury'}</t>
+          <t>Injury</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'reporting',_'value':_'reporting'}</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Reporting', 'value': 'Reporting'}</t>
+          <t>Reporting</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'investigation',_'value':_'investigation'}</t>
+          <t>investigation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Investigation', 'value': 'Investigation'}</t>
+          <t>Investigation</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'corrective_action',_'value':_'corrective_action'}</t>
+          <t>corrective_action</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Corrective action', 'value': 'Corrective action'}</t>
+          <t>Corrective action</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'video',_'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Video', 'value': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'presentation',_'value':_'presentation'}</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Presentation', 'value': 'Presentation'}</t>
+          <t>Presentation</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'manual',_'value':_'manual'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Manual', 'value': 'Manual'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'effective',_'value':_'effective'}</t>
+          <t>effective</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Effective', 'value': 'Effective'}</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'not_effective',_'value':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Not effective', 'value': 'Not effective'}</t>
+          <t>Not effective</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_effective',_'value':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat effective', 'value': 'Somewhat effective'}</t>
+          <t>Somewhat effective</t>
         </is>
       </c>
     </row>
